--- a/testakten/familienrecht-zugewinn-kryptowerte-ferienwohnung-passau/xlsx/zugewinn_arbeitsmatrix.xlsx
+++ b/testakten/familienrecht-zugewinn-kryptowerte-ferienwohnung-passau/xlsx/zugewinn_arbeitsmatrix.xlsx
@@ -432,12 +432,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Anfangsvermoegen</t>
+          <t>Anfangsvermögen</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Endvermoegen</t>
+          <t>Endvermögen</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
